--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/02,07,26 ПОКОМ ЗПФ/дв 02,07,26 лгрсч пок зпф.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/02,07,26 ПОКОМ ЗПФ/дв 02,07,26 лгрсч пок зпф.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\02,07,26 ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487D02F9-E9E0-487B-8811-828A6CB4AD64}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B8E9974-40F5-4B52-AB52-4F413A8B8972}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AH$67</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -23686,7 +23686,7 @@
     <col min="31" max="31" width="6" customWidth="1"/>
     <col min="32" max="33" width="5" customWidth="1"/>
     <col min="34" max="34" width="6" style="11" customWidth="1"/>
-    <col min="35" max="35" width="3" customWidth="1"/>
+    <col min="35" max="35" width="7.42578125" customWidth="1"/>
     <col min="36" max="38" width="6.5703125" customWidth="1"/>
     <col min="39" max="49" width="3" customWidth="1"/>
   </cols>
@@ -24078,7 +24078,10 @@
         <f>SUM(AH6:AH498)</f>
         <v>18.207142857142852</v>
       </c>
-      <c r="AI5" s="16"/>
+      <c r="AI5" s="3">
+        <f>SUM(AI6:AI498)</f>
+        <v>1503.8320000000001</v>
+      </c>
       <c r="AJ5" s="16"/>
       <c r="AK5" s="16"/>
       <c r="AL5" s="16"/>
@@ -24173,7 +24176,10 @@
       <c r="AF6" s="12"/>
       <c r="AG6" s="12"/>
       <c r="AH6" s="15"/>
-      <c r="AI6" s="16"/>
+      <c r="AI6" s="16">
+        <f>P6*G6</f>
+        <v>0</v>
+      </c>
       <c r="AJ6" s="16"/>
       <c r="AK6" s="16"/>
       <c r="AL6" s="16"/>
@@ -24266,7 +24272,10 @@
       <c r="AF7" s="12"/>
       <c r="AG7" s="12"/>
       <c r="AH7" s="15"/>
-      <c r="AI7" s="16"/>
+      <c r="AI7" s="16">
+        <f t="shared" ref="AI7:AI67" si="6">P7*G7</f>
+        <v>0</v>
+      </c>
       <c r="AJ7" s="16"/>
       <c r="AK7" s="16"/>
       <c r="AL7" s="16"/>
@@ -24359,7 +24368,10 @@
       <c r="AF8" s="12"/>
       <c r="AG8" s="12"/>
       <c r="AH8" s="15"/>
-      <c r="AI8" s="16"/>
+      <c r="AI8" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AJ8" s="16"/>
       <c r="AK8" s="16"/>
       <c r="AL8" s="16"/>
@@ -24423,7 +24435,7 @@
         <v>100</v>
       </c>
       <c r="R9" s="4">
-        <f t="shared" ref="R9:R18" si="6">AC9*AD9</f>
+        <f t="shared" ref="R9:R18" si="7">AC9*AD9</f>
         <v>168</v>
       </c>
       <c r="S9" s="16">
@@ -24454,7 +24466,7 @@
       </c>
       <c r="AA9" s="16"/>
       <c r="AB9" s="16">
-        <f t="shared" ref="AB9:AB18" si="7">G9*Q9</f>
+        <f t="shared" ref="AB9:AB18" si="8">G9*Q9</f>
         <v>22</v>
       </c>
       <c r="AC9" s="6">
@@ -24462,11 +24474,11 @@
         <v>12</v>
       </c>
       <c r="AD9" s="8">
-        <f t="shared" ref="AD9:AD18" si="8">MROUND(Q9, AC9*AF9)/AC9</f>
+        <f t="shared" ref="AD9:AD18" si="9">MROUND(Q9, AC9*AF9)/AC9</f>
         <v>14</v>
       </c>
       <c r="AE9" s="16">
-        <f t="shared" ref="AE9:AE18" si="9">AD9*AC9*G9</f>
+        <f t="shared" ref="AE9:AE18" si="10">AD9*AC9*G9</f>
         <v>36.96</v>
       </c>
       <c r="AF9" s="16">
@@ -24478,10 +24490,13 @@
         <v>70</v>
       </c>
       <c r="AH9" s="8">
-        <f t="shared" ref="AH9:AH18" si="10">AD9/AG9</f>
+        <f t="shared" ref="AH9:AH18" si="11">AD9/AG9</f>
         <v>0.2</v>
       </c>
-      <c r="AI9" s="16"/>
+      <c r="AI9" s="16">
+        <f t="shared" si="6"/>
+        <v>0.22</v>
+      </c>
       <c r="AJ9" s="16"/>
       <c r="AK9" s="16"/>
       <c r="AL9" s="16"/>
@@ -24548,7 +24563,7 @@
         <v>97.199999999999989</v>
       </c>
       <c r="R10" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>168</v>
       </c>
       <c r="S10" s="16">
@@ -24579,7 +24594,7 @@
       </c>
       <c r="AA10" s="16"/>
       <c r="AB10" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>29.159999999999997</v>
       </c>
       <c r="AC10" s="6">
@@ -24587,11 +24602,11 @@
         <v>12</v>
       </c>
       <c r="AD10" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
       <c r="AE10" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>50.4</v>
       </c>
       <c r="AF10" s="16">
@@ -24603,10 +24618,13 @@
         <v>70</v>
       </c>
       <c r="AH10" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
-      <c r="AI10" s="16"/>
+      <c r="AI10" s="16">
+        <f t="shared" si="6"/>
+        <v>5.52</v>
+      </c>
       <c r="AJ10" s="16"/>
       <c r="AK10" s="16"/>
       <c r="AL10" s="16"/>
@@ -24673,7 +24691,7 @@
         <v>728.39999999999986</v>
       </c>
       <c r="R11" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>756</v>
       </c>
       <c r="S11" s="16">
@@ -24704,7 +24722,7 @@
       </c>
       <c r="AA11" s="16"/>
       <c r="AB11" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>203.95199999999997</v>
       </c>
       <c r="AC11" s="6">
@@ -24712,11 +24730,11 @@
         <v>6</v>
       </c>
       <c r="AD11" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>126</v>
       </c>
       <c r="AE11" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>211.68</v>
       </c>
       <c r="AF11" s="16">
@@ -24728,10 +24746,13 @@
         <v>140</v>
       </c>
       <c r="AH11" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.9</v>
       </c>
-      <c r="AI11" s="16"/>
+      <c r="AI11" s="16">
+        <f t="shared" si="6"/>
+        <v>37.520000000000003</v>
+      </c>
       <c r="AJ11" s="16"/>
       <c r="AK11" s="16"/>
       <c r="AL11" s="16"/>
@@ -24794,11 +24815,11 @@
         <v>71.599999999999994</v>
       </c>
       <c r="Q12" s="4">
-        <f t="shared" ref="Q12:Q18" si="11">14*P12-O12-F12</f>
+        <f t="shared" ref="Q12:Q18" si="12">14*P12-O12-F12</f>
         <v>289.39999999999986</v>
       </c>
       <c r="R12" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>336</v>
       </c>
       <c r="S12" s="16">
@@ -24829,7 +24850,7 @@
       </c>
       <c r="AA12" s="16"/>
       <c r="AB12" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>69.45599999999996</v>
       </c>
       <c r="AC12" s="6">
@@ -24837,11 +24858,11 @@
         <v>12</v>
       </c>
       <c r="AD12" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>28</v>
       </c>
       <c r="AE12" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>80.64</v>
       </c>
       <c r="AF12" s="16">
@@ -24853,10 +24874,13 @@
         <v>70</v>
       </c>
       <c r="AH12" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.4</v>
       </c>
-      <c r="AI12" s="16"/>
+      <c r="AI12" s="16">
+        <f t="shared" si="6"/>
+        <v>17.183999999999997</v>
+      </c>
       <c r="AJ12" s="16"/>
       <c r="AK12" s="16"/>
       <c r="AL12" s="16"/>
@@ -24920,7 +24944,7 @@
       </c>
       <c r="Q13" s="4"/>
       <c r="R13" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S13" s="16">
@@ -24951,7 +24975,7 @@
       </c>
       <c r="AA13" s="16"/>
       <c r="AB13" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AC13" s="6">
@@ -24959,11 +24983,11 @@
         <v>12</v>
       </c>
       <c r="AD13" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AE13" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AF13" s="16">
@@ -24975,10 +24999,13 @@
         <v>70</v>
       </c>
       <c r="AH13" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AI13" s="16"/>
+      <c r="AI13" s="16">
+        <f t="shared" si="6"/>
+        <v>14.928000000000001</v>
+      </c>
       <c r="AJ13" s="16"/>
       <c r="AK13" s="16"/>
       <c r="AL13" s="16"/>
@@ -25041,11 +25068,11 @@
         <v>62.8</v>
       </c>
       <c r="Q14" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>185.19999999999993</v>
       </c>
       <c r="R14" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>168</v>
       </c>
       <c r="S14" s="16">
@@ -25076,7 +25103,7 @@
       </c>
       <c r="AA14" s="16"/>
       <c r="AB14" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>44.447999999999979</v>
       </c>
       <c r="AC14" s="6">
@@ -25084,11 +25111,11 @@
         <v>12</v>
       </c>
       <c r="AD14" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
       <c r="AE14" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>40.32</v>
       </c>
       <c r="AF14" s="16">
@@ -25100,10 +25127,13 @@
         <v>70</v>
       </c>
       <c r="AH14" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
-      <c r="AI14" s="16"/>
+      <c r="AI14" s="16">
+        <f t="shared" si="6"/>
+        <v>15.071999999999999</v>
+      </c>
       <c r="AJ14" s="16"/>
       <c r="AK14" s="16"/>
       <c r="AL14" s="16"/>
@@ -25174,7 +25204,7 @@
         <v>1165.6999999999998</v>
       </c>
       <c r="R15" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1176</v>
       </c>
       <c r="S15" s="16">
@@ -25205,7 +25235,7 @@
       </c>
       <c r="AA15" s="16"/>
       <c r="AB15" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>279.76799999999997</v>
       </c>
       <c r="AC15" s="6">
@@ -25213,11 +25243,11 @@
         <v>12</v>
       </c>
       <c r="AD15" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>98</v>
       </c>
       <c r="AE15" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>282.24</v>
       </c>
       <c r="AF15" s="16">
@@ -25229,10 +25259,13 @@
         <v>70</v>
       </c>
       <c r="AH15" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.4</v>
       </c>
-      <c r="AI15" s="16"/>
+      <c r="AI15" s="16">
+        <f t="shared" si="6"/>
+        <v>52.08</v>
+      </c>
       <c r="AJ15" s="16"/>
       <c r="AK15" s="16"/>
       <c r="AL15" s="16"/>
@@ -25296,7 +25329,7 @@
       </c>
       <c r="Q16" s="4"/>
       <c r="R16" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S16" s="16">
@@ -25327,7 +25360,7 @@
       </c>
       <c r="AA16" s="16"/>
       <c r="AB16" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AC16" s="6">
@@ -25335,11 +25368,11 @@
         <v>8</v>
       </c>
       <c r="AD16" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AE16" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AF16" s="16">
@@ -25351,10 +25384,13 @@
         <v>70</v>
       </c>
       <c r="AH16" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AI16" s="16"/>
+      <c r="AI16" s="16">
+        <f t="shared" si="6"/>
+        <v>9.7919999999999998</v>
+      </c>
       <c r="AJ16" s="16"/>
       <c r="AK16" s="16"/>
       <c r="AL16" s="16"/>
@@ -25421,7 +25457,7 @@
         <v>894.11999999999989</v>
       </c>
       <c r="R17" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1008</v>
       </c>
       <c r="S17" s="16">
@@ -25452,7 +25488,7 @@
       </c>
       <c r="AA17" s="16"/>
       <c r="AB17" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>80.470799999999983</v>
       </c>
       <c r="AC17" s="6">
@@ -25460,11 +25496,11 @@
         <v>24</v>
       </c>
       <c r="AD17" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>42</v>
       </c>
       <c r="AE17" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>90.72</v>
       </c>
       <c r="AF17" s="16">
@@ -25476,10 +25512,13 @@
         <v>126</v>
       </c>
       <c r="AH17" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AI17" s="16"/>
+      <c r="AI17" s="16">
+        <f t="shared" si="6"/>
+        <v>10.368</v>
+      </c>
       <c r="AJ17" s="16"/>
       <c r="AK17" s="16"/>
       <c r="AL17" s="16"/>
@@ -25542,11 +25581,11 @@
         <v>92.6</v>
       </c>
       <c r="Q18" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>388.39999999999986</v>
       </c>
       <c r="R18" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>420</v>
       </c>
       <c r="S18" s="16">
@@ -25577,7 +25616,7 @@
       </c>
       <c r="AA18" s="16"/>
       <c r="AB18" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>139.82399999999996</v>
       </c>
       <c r="AC18" s="6">
@@ -25585,11 +25624,11 @@
         <v>10</v>
       </c>
       <c r="AD18" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>42</v>
       </c>
       <c r="AE18" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>151.19999999999999</v>
       </c>
       <c r="AF18" s="16">
@@ -25601,10 +25640,13 @@
         <v>70</v>
       </c>
       <c r="AH18" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.6</v>
       </c>
-      <c r="AI18" s="16"/>
+      <c r="AI18" s="16">
+        <f t="shared" si="6"/>
+        <v>33.335999999999999</v>
+      </c>
       <c r="AJ18" s="16"/>
       <c r="AK18" s="16"/>
       <c r="AL18" s="16"/>
@@ -25695,7 +25737,10 @@
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
       <c r="AH19" s="15"/>
-      <c r="AI19" s="16"/>
+      <c r="AI19" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AJ19" s="16"/>
       <c r="AK19" s="16"/>
       <c r="AL19" s="16"/>
@@ -25759,11 +25804,11 @@
         <v>56.8</v>
       </c>
       <c r="Q20" s="4">
-        <f t="shared" ref="Q20:Q40" si="12">14*P20-O20-F20</f>
+        <f t="shared" ref="Q20:Q40" si="13">14*P20-O20-F20</f>
         <v>543.19999999999993</v>
       </c>
       <c r="R20" s="4">
-        <f t="shared" ref="R20:R42" si="13">AC20*AD20</f>
+        <f t="shared" ref="R20:R42" si="14">AC20*AD20</f>
         <v>504</v>
       </c>
       <c r="S20" s="16">
@@ -25794,7 +25839,7 @@
       </c>
       <c r="AA20" s="16"/>
       <c r="AB20" s="16">
-        <f t="shared" ref="AB20:AB42" si="14">G20*Q20</f>
+        <f t="shared" ref="AB20:AB42" si="15">G20*Q20</f>
         <v>108.63999999999999</v>
       </c>
       <c r="AC20" s="6">
@@ -25802,11 +25847,11 @@
         <v>12</v>
       </c>
       <c r="AD20" s="8">
-        <f t="shared" ref="AD20:AD42" si="15">MROUND(Q20, AC20*AF20)/AC20</f>
+        <f t="shared" ref="AD20:AD42" si="16">MROUND(Q20, AC20*AF20)/AC20</f>
         <v>42</v>
       </c>
       <c r="AE20" s="16">
-        <f t="shared" ref="AE20:AE42" si="16">AD20*AC20*G20</f>
+        <f t="shared" ref="AE20:AE42" si="17">AD20*AC20*G20</f>
         <v>100.80000000000001</v>
       </c>
       <c r="AF20" s="16">
@@ -25818,10 +25863,13 @@
         <v>70</v>
       </c>
       <c r="AH20" s="8">
-        <f t="shared" ref="AH20:AH42" si="17">AD20/AG20</f>
+        <f t="shared" ref="AH20:AH42" si="18">AD20/AG20</f>
         <v>0.6</v>
       </c>
-      <c r="AI20" s="16"/>
+      <c r="AI20" s="16">
+        <f t="shared" si="6"/>
+        <v>11.36</v>
+      </c>
       <c r="AJ20" s="16"/>
       <c r="AK20" s="16"/>
       <c r="AL20" s="16"/>
@@ -25884,11 +25932,11 @@
         <v>81.8</v>
       </c>
       <c r="Q21" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>349.20000000000005</v>
       </c>
       <c r="R21" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>336</v>
       </c>
       <c r="S21" s="16">
@@ -25919,7 +25967,7 @@
       </c>
       <c r="AA21" s="16"/>
       <c r="AB21" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>69.840000000000018</v>
       </c>
       <c r="AC21" s="6">
@@ -25927,11 +25975,11 @@
         <v>12</v>
       </c>
       <c r="AD21" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>28</v>
       </c>
       <c r="AE21" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>67.2</v>
       </c>
       <c r="AF21" s="16">
@@ -25943,10 +25991,13 @@
         <v>70</v>
       </c>
       <c r="AH21" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.4</v>
       </c>
-      <c r="AI21" s="16"/>
+      <c r="AI21" s="16">
+        <f t="shared" si="6"/>
+        <v>16.36</v>
+      </c>
       <c r="AJ21" s="16"/>
       <c r="AK21" s="16"/>
       <c r="AL21" s="16"/>
@@ -26013,7 +26064,7 @@
         <v>380.31999999999988</v>
       </c>
       <c r="R22" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>360</v>
       </c>
       <c r="S22" s="16">
@@ -26044,7 +26095,7 @@
       </c>
       <c r="AA22" s="16"/>
       <c r="AB22" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>380.31999999999988</v>
       </c>
       <c r="AC22" s="6">
@@ -26052,11 +26103,11 @@
         <v>5</v>
       </c>
       <c r="AD22" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>72</v>
       </c>
       <c r="AE22" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>360</v>
       </c>
       <c r="AF22" s="16">
@@ -26068,10 +26119,13 @@
         <v>84</v>
       </c>
       <c r="AH22" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.8571428571428571</v>
       </c>
-      <c r="AI22" s="16"/>
+      <c r="AI22" s="16">
+        <f t="shared" si="6"/>
+        <v>39.739999999999995</v>
+      </c>
       <c r="AJ22" s="16"/>
       <c r="AK22" s="16"/>
       <c r="AL22" s="16"/>
@@ -26131,11 +26185,11 @@
         <v>28.5</v>
       </c>
       <c r="Q23" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>57</v>
       </c>
       <c r="R23" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>66</v>
       </c>
       <c r="S23" s="16">
@@ -26166,18 +26220,18 @@
       </c>
       <c r="AA23" s="16"/>
       <c r="AB23" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>57</v>
       </c>
       <c r="AC23" s="6">
         <v>5.5</v>
       </c>
       <c r="AD23" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="AE23" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>66</v>
       </c>
       <c r="AF23" s="16">
@@ -26187,10 +26241,13 @@
         <v>84</v>
       </c>
       <c r="AH23" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AI23" s="16"/>
+      <c r="AI23" s="16">
+        <f t="shared" si="6"/>
+        <v>28.5</v>
+      </c>
       <c r="AJ23" s="16"/>
       <c r="AK23" s="16"/>
       <c r="AL23" s="16"/>
@@ -26256,7 +26313,7 @@
       </c>
       <c r="Q24" s="4"/>
       <c r="R24" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S24" s="16">
@@ -26287,7 +26344,7 @@
       </c>
       <c r="AA24" s="16"/>
       <c r="AB24" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AC24" s="6">
@@ -26295,11 +26352,11 @@
         <v>3</v>
       </c>
       <c r="AD24" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE24" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF24" s="16">
@@ -26311,10 +26368,13 @@
         <v>126</v>
       </c>
       <c r="AH24" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AI24" s="16"/>
+      <c r="AI24" s="16">
+        <f t="shared" si="6"/>
+        <v>31.8</v>
+      </c>
       <c r="AJ24" s="16"/>
       <c r="AK24" s="16"/>
       <c r="AL24" s="16"/>
@@ -26375,11 +26435,11 @@
         <v>36.6</v>
       </c>
       <c r="Q25" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>92.399999999999977</v>
       </c>
       <c r="R25" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>84</v>
       </c>
       <c r="S25" s="16">
@@ -26410,7 +26470,7 @@
       </c>
       <c r="AA25" s="16"/>
       <c r="AB25" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>23.099999999999994</v>
       </c>
       <c r="AC25" s="6">
@@ -26418,11 +26478,11 @@
         <v>6</v>
       </c>
       <c r="AD25" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>14</v>
       </c>
       <c r="AE25" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>21</v>
       </c>
       <c r="AF25" s="16">
@@ -26434,10 +26494,13 @@
         <v>140</v>
       </c>
       <c r="AH25" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.1</v>
       </c>
-      <c r="AI25" s="16"/>
+      <c r="AI25" s="16">
+        <f t="shared" si="6"/>
+        <v>9.15</v>
+      </c>
       <c r="AJ25" s="16"/>
       <c r="AK25" s="16"/>
       <c r="AL25" s="16"/>
@@ -26501,7 +26564,7 @@
       </c>
       <c r="Q26" s="4"/>
       <c r="R26" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S26" s="16">
@@ -26532,7 +26595,7 @@
       </c>
       <c r="AA26" s="16"/>
       <c r="AB26" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AC26" s="6">
@@ -26540,11 +26603,11 @@
         <v>6</v>
       </c>
       <c r="AD26" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE26" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF26" s="16">
@@ -26556,10 +26619,13 @@
         <v>140</v>
       </c>
       <c r="AH26" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AI26" s="16"/>
+      <c r="AI26" s="16">
+        <f t="shared" si="6"/>
+        <v>13.55</v>
+      </c>
       <c r="AJ26" s="16"/>
       <c r="AK26" s="16"/>
       <c r="AL26" s="16"/>
@@ -26622,11 +26688,11 @@
         <v>79</v>
       </c>
       <c r="Q27" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>235</v>
       </c>
       <c r="R27" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>216</v>
       </c>
       <c r="S27" s="16">
@@ -26657,7 +26723,7 @@
       </c>
       <c r="AA27" s="16"/>
       <c r="AB27" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>235</v>
       </c>
       <c r="AC27" s="6">
@@ -26665,11 +26731,11 @@
         <v>6</v>
       </c>
       <c r="AD27" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>36</v>
       </c>
       <c r="AE27" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>216</v>
       </c>
       <c r="AF27" s="16">
@@ -26681,10 +26747,13 @@
         <v>84</v>
       </c>
       <c r="AH27" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="AI27" s="16"/>
+      <c r="AI27" s="16">
+        <f t="shared" si="6"/>
+        <v>79</v>
+      </c>
       <c r="AJ27" s="16"/>
       <c r="AK27" s="16"/>
       <c r="AL27" s="16"/>
@@ -26750,7 +26819,7 @@
       </c>
       <c r="Q28" s="4"/>
       <c r="R28" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S28" s="16">
@@ -26781,7 +26850,7 @@
       </c>
       <c r="AA28" s="16"/>
       <c r="AB28" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AC28" s="6">
@@ -26789,11 +26858,11 @@
         <v>12</v>
       </c>
       <c r="AD28" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE28" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF28" s="16">
@@ -26805,10 +26874,13 @@
         <v>70</v>
       </c>
       <c r="AH28" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AI28" s="16"/>
+      <c r="AI28" s="16">
+        <f t="shared" si="6"/>
+        <v>5.2440000000000007</v>
+      </c>
       <c r="AJ28" s="16"/>
       <c r="AK28" s="16"/>
       <c r="AL28" s="16"/>
@@ -26875,7 +26947,7 @@
         <v>417.57999999999993</v>
       </c>
       <c r="R29" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>336</v>
       </c>
       <c r="S29" s="16">
@@ -26906,7 +26978,7 @@
       </c>
       <c r="AA29" s="16"/>
       <c r="AB29" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>104.39499999999998</v>
       </c>
       <c r="AC29" s="6">
@@ -26914,11 +26986,11 @@
         <v>12</v>
       </c>
       <c r="AD29" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>28</v>
       </c>
       <c r="AE29" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>84</v>
       </c>
       <c r="AF29" s="16">
@@ -26930,10 +27002,13 @@
         <v>70</v>
       </c>
       <c r="AH29" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.4</v>
       </c>
-      <c r="AI29" s="16"/>
+      <c r="AI29" s="16">
+        <f t="shared" si="6"/>
+        <v>25.45</v>
+      </c>
       <c r="AJ29" s="16"/>
       <c r="AK29" s="16"/>
       <c r="AL29" s="16"/>
@@ -27000,7 +27075,7 @@
         <v>139</v>
       </c>
       <c r="R30" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>168</v>
       </c>
       <c r="S30" s="16">
@@ -27031,7 +27106,7 @@
       </c>
       <c r="AA30" s="16"/>
       <c r="AB30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>34.75</v>
       </c>
       <c r="AC30" s="6">
@@ -27039,11 +27114,11 @@
         <v>12</v>
       </c>
       <c r="AD30" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>14</v>
       </c>
       <c r="AE30" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>42</v>
       </c>
       <c r="AF30" s="16">
@@ -27055,10 +27130,13 @@
         <v>70</v>
       </c>
       <c r="AH30" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.2</v>
       </c>
-      <c r="AI30" s="16"/>
+      <c r="AI30" s="16">
+        <f t="shared" si="6"/>
+        <v>18.899999999999999</v>
+      </c>
       <c r="AJ30" s="16"/>
       <c r="AK30" s="16"/>
       <c r="AL30" s="16"/>
@@ -27127,7 +27205,7 @@
         <v>702.59999999999991</v>
       </c>
       <c r="R31" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>672</v>
       </c>
       <c r="S31" s="16">
@@ -27158,7 +27236,7 @@
       </c>
       <c r="AA31" s="16"/>
       <c r="AB31" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>175.64999999999998</v>
       </c>
       <c r="AC31" s="6">
@@ -27166,11 +27244,11 @@
         <v>12</v>
       </c>
       <c r="AD31" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>56</v>
       </c>
       <c r="AE31" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>168</v>
       </c>
       <c r="AF31" s="16">
@@ -27182,10 +27260,13 @@
         <v>70</v>
       </c>
       <c r="AH31" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.8</v>
       </c>
-      <c r="AI31" s="16"/>
+      <c r="AI31" s="16">
+        <f t="shared" si="6"/>
+        <v>17.899999999999999</v>
+      </c>
       <c r="AJ31" s="16"/>
       <c r="AK31" s="16"/>
       <c r="AL31" s="16"/>
@@ -27249,7 +27330,7 @@
       </c>
       <c r="Q32" s="4"/>
       <c r="R32" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S32" s="16">
@@ -27280,7 +27361,7 @@
       </c>
       <c r="AA32" s="16"/>
       <c r="AB32" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AC32" s="6">
@@ -27288,11 +27369,11 @@
         <v>12</v>
       </c>
       <c r="AD32" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE32" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF32" s="16">
@@ -27304,10 +27385,13 @@
         <v>70</v>
       </c>
       <c r="AH32" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AI32" s="16"/>
+      <c r="AI32" s="16">
+        <f t="shared" si="6"/>
+        <v>0.65</v>
+      </c>
       <c r="AJ32" s="16"/>
       <c r="AK32" s="16"/>
       <c r="AL32" s="16"/>
@@ -27370,11 +27454,11 @@
         <v>36.4</v>
       </c>
       <c r="Q33" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>245.59999999999997</v>
       </c>
       <c r="R33" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>288</v>
       </c>
       <c r="S33" s="16">
@@ -27405,7 +27489,7 @@
       </c>
       <c r="AA33" s="16"/>
       <c r="AB33" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>171.91999999999996</v>
       </c>
       <c r="AC33" s="6">
@@ -27413,11 +27497,11 @@
         <v>8</v>
       </c>
       <c r="AD33" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>36</v>
       </c>
       <c r="AE33" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>201.6</v>
       </c>
       <c r="AF33" s="16">
@@ -27429,10 +27513,13 @@
         <v>84</v>
       </c>
       <c r="AH33" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="AI33" s="16"/>
+      <c r="AI33" s="16">
+        <f t="shared" si="6"/>
+        <v>25.479999999999997</v>
+      </c>
       <c r="AJ33" s="16"/>
       <c r="AK33" s="16"/>
       <c r="AL33" s="16"/>
@@ -27499,7 +27586,7 @@
         <v>69</v>
       </c>
       <c r="R34" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>96</v>
       </c>
       <c r="S34" s="16">
@@ -27530,7 +27617,7 @@
       </c>
       <c r="AA34" s="16"/>
       <c r="AB34" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>48.3</v>
       </c>
       <c r="AC34" s="6">
@@ -27538,11 +27625,11 @@
         <v>8</v>
       </c>
       <c r="AD34" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="AE34" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>67.199999999999989</v>
       </c>
       <c r="AF34" s="16">
@@ -27554,10 +27641,13 @@
         <v>84</v>
       </c>
       <c r="AH34" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AI34" s="16"/>
+      <c r="AI34" s="16">
+        <f t="shared" si="6"/>
+        <v>16.52</v>
+      </c>
       <c r="AJ34" s="16"/>
       <c r="AK34" s="16"/>
       <c r="AL34" s="16"/>
@@ -27621,7 +27711,7 @@
       </c>
       <c r="Q35" s="4"/>
       <c r="R35" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S35" s="16">
@@ -27652,7 +27742,7 @@
       </c>
       <c r="AA35" s="16"/>
       <c r="AB35" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AC35" s="6">
@@ -27660,11 +27750,11 @@
         <v>8</v>
       </c>
       <c r="AD35" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE35" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF35" s="16">
@@ -27676,10 +27766,13 @@
         <v>84</v>
       </c>
       <c r="AH35" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AI35" s="16"/>
+      <c r="AI35" s="16">
+        <f t="shared" si="6"/>
+        <v>12.179999999999998</v>
+      </c>
       <c r="AJ35" s="16"/>
       <c r="AK35" s="16"/>
       <c r="AL35" s="16"/>
@@ -27745,7 +27838,7 @@
       </c>
       <c r="Q36" s="4"/>
       <c r="R36" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S36" s="16">
@@ -27778,7 +27871,7 @@
         <v>57</v>
       </c>
       <c r="AB36" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AC36" s="6">
@@ -27786,11 +27879,11 @@
         <v>10</v>
       </c>
       <c r="AD36" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE36" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF36" s="16">
@@ -27802,10 +27895,13 @@
         <v>84</v>
       </c>
       <c r="AH36" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AI36" s="16"/>
+      <c r="AI36" s="16">
+        <f t="shared" si="6"/>
+        <v>6.72</v>
+      </c>
       <c r="AJ36" s="16"/>
       <c r="AK36" s="16"/>
       <c r="AL36" s="16"/>
@@ -27874,7 +27970,7 @@
         <v>63.599999999999994</v>
       </c>
       <c r="R37" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>120</v>
       </c>
       <c r="S37" s="16">
@@ -27905,7 +28001,7 @@
       </c>
       <c r="AA37" s="16"/>
       <c r="AB37" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>44.519999999999996</v>
       </c>
       <c r="AC37" s="6">
@@ -27913,11 +28009,11 @@
         <v>10</v>
       </c>
       <c r="AD37" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="AE37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>84</v>
       </c>
       <c r="AF37" s="16">
@@ -27929,10 +28025,13 @@
         <v>84</v>
       </c>
       <c r="AH37" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AI37" s="16"/>
+      <c r="AI37" s="16">
+        <f t="shared" si="6"/>
+        <v>10.219999999999999</v>
+      </c>
       <c r="AJ37" s="16"/>
       <c r="AK37" s="16"/>
       <c r="AL37" s="16"/>
@@ -27984,7 +28083,7 @@
         <v>198</v>
       </c>
       <c r="L38" s="16">
-        <f t="shared" ref="L38:L67" si="18">E38-K38</f>
+        <f t="shared" ref="L38:L67" si="19">E38-K38</f>
         <v>-8</v>
       </c>
       <c r="M38" s="16"/>
@@ -27993,23 +28092,23 @@
         <v>360</v>
       </c>
       <c r="P38" s="16">
-        <f t="shared" ref="P38:P67" si="19">E38/5</f>
+        <f t="shared" ref="P38:P67" si="20">E38/5</f>
         <v>38</v>
       </c>
       <c r="Q38" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>145</v>
       </c>
       <c r="R38" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>120</v>
       </c>
       <c r="S38" s="16">
-        <f t="shared" ref="S38:S67" si="20">(F38+O38+R38)/P38</f>
+        <f t="shared" ref="S38:S67" si="21">(F38+O38+R38)/P38</f>
         <v>13.342105263157896</v>
       </c>
       <c r="T38" s="16">
-        <f t="shared" ref="T38:T67" si="21">(F38+O38)/P38</f>
+        <f t="shared" ref="T38:T67" si="22">(F38+O38)/P38</f>
         <v>10.184210526315789</v>
       </c>
       <c r="U38" s="16">
@@ -28032,7 +28131,7 @@
       </c>
       <c r="AA38" s="16"/>
       <c r="AB38" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>101.5</v>
       </c>
       <c r="AC38" s="6">
@@ -28040,11 +28139,11 @@
         <v>10</v>
       </c>
       <c r="AD38" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="AE38" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>84</v>
       </c>
       <c r="AF38" s="16">
@@ -28056,10 +28155,13 @@
         <v>84</v>
       </c>
       <c r="AH38" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AI38" s="16"/>
+      <c r="AI38" s="16">
+        <f t="shared" si="6"/>
+        <v>26.599999999999998</v>
+      </c>
       <c r="AJ38" s="16"/>
       <c r="AK38" s="16"/>
       <c r="AL38" s="16"/>
@@ -28109,7 +28211,7 @@
         <v>75</v>
       </c>
       <c r="L39" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M39" s="16"/>
@@ -28118,7 +28220,7 @@
         <v>120</v>
       </c>
       <c r="P39" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>15</v>
       </c>
       <c r="Q39" s="4">
@@ -28126,15 +28228,15 @@
         <v>62</v>
       </c>
       <c r="R39" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>120</v>
       </c>
       <c r="S39" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>19.866666666666667</v>
       </c>
       <c r="T39" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>11.866666666666667</v>
       </c>
       <c r="U39" s="16">
@@ -28157,7 +28259,7 @@
       </c>
       <c r="AA39" s="16"/>
       <c r="AB39" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>43.4</v>
       </c>
       <c r="AC39" s="6">
@@ -28165,11 +28267,11 @@
         <v>10</v>
       </c>
       <c r="AD39" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="AE39" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>84</v>
       </c>
       <c r="AF39" s="16">
@@ -28181,10 +28283,13 @@
         <v>84</v>
       </c>
       <c r="AH39" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AI39" s="16"/>
+      <c r="AI39" s="16">
+        <f t="shared" si="6"/>
+        <v>10.5</v>
+      </c>
       <c r="AJ39" s="16"/>
       <c r="AK39" s="16"/>
       <c r="AL39" s="16"/>
@@ -28236,7 +28341,7 @@
         <v>466.4</v>
       </c>
       <c r="L40" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-6.3999999999999773</v>
       </c>
       <c r="M40" s="16"/>
@@ -28245,23 +28350,23 @@
         <v>360</v>
       </c>
       <c r="P40" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>92</v>
       </c>
       <c r="Q40" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>668</v>
       </c>
       <c r="R40" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>660</v>
       </c>
       <c r="S40" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>13.913043478260869</v>
       </c>
       <c r="T40" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>6.7391304347826084</v>
       </c>
       <c r="U40" s="16">
@@ -28284,7 +28389,7 @@
       </c>
       <c r="AA40" s="16"/>
       <c r="AB40" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>668</v>
       </c>
       <c r="AC40" s="6">
@@ -28292,11 +28397,11 @@
         <v>5</v>
       </c>
       <c r="AD40" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>132</v>
       </c>
       <c r="AE40" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>660</v>
       </c>
       <c r="AF40" s="16">
@@ -28308,10 +28413,13 @@
         <v>144</v>
       </c>
       <c r="AH40" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.91666666666666663</v>
       </c>
-      <c r="AI40" s="16"/>
+      <c r="AI40" s="16">
+        <f t="shared" si="6"/>
+        <v>92</v>
+      </c>
       <c r="AJ40" s="16"/>
       <c r="AK40" s="16"/>
       <c r="AL40" s="16"/>
@@ -28361,7 +28469,7 @@
         <v>186</v>
       </c>
       <c r="L41" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-25</v>
       </c>
       <c r="M41" s="16"/>
@@ -28370,22 +28478,22 @@
         <v>384</v>
       </c>
       <c r="P41" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>32.200000000000003</v>
       </c>
       <c r="Q41" s="4"/>
       <c r="R41" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S41" s="16">
-        <f t="shared" si="20"/>
-        <v>15.93167701863354</v>
-      </c>
-      <c r="T41" s="16">
         <f t="shared" si="21"/>
         <v>15.93167701863354</v>
       </c>
+      <c r="T41" s="16">
+        <f t="shared" si="22"/>
+        <v>15.93167701863354</v>
+      </c>
       <c r="U41" s="16">
         <v>61.8</v>
       </c>
@@ -28406,7 +28514,7 @@
       </c>
       <c r="AA41" s="16"/>
       <c r="AB41" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AC41" s="6">
@@ -28414,11 +28522,11 @@
         <v>16</v>
       </c>
       <c r="AD41" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE41" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF41" s="16">
@@ -28430,10 +28538,13 @@
         <v>84</v>
       </c>
       <c r="AH41" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AI41" s="16"/>
+      <c r="AI41" s="16">
+        <f t="shared" si="6"/>
+        <v>12.880000000000003</v>
+      </c>
       <c r="AJ41" s="16"/>
       <c r="AK41" s="16"/>
       <c r="AL41" s="16"/>
@@ -28485,7 +28596,7 @@
         <v>266</v>
       </c>
       <c r="L42" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M42" s="16"/>
@@ -28494,7 +28605,7 @@
         <v>480</v>
       </c>
       <c r="P42" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>53.2</v>
       </c>
       <c r="Q42" s="4">
@@ -28502,15 +28613,15 @@
         <v>95</v>
       </c>
       <c r="R42" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>120</v>
       </c>
       <c r="S42" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>15.469924812030074</v>
       </c>
       <c r="T42" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>13.214285714285714</v>
       </c>
       <c r="U42" s="16">
@@ -28533,7 +28644,7 @@
       </c>
       <c r="AA42" s="16"/>
       <c r="AB42" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>66.5</v>
       </c>
       <c r="AC42" s="6">
@@ -28541,11 +28652,11 @@
         <v>10</v>
       </c>
       <c r="AD42" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="AE42" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>84</v>
       </c>
       <c r="AF42" s="16">
@@ -28557,10 +28668,13 @@
         <v>84</v>
       </c>
       <c r="AH42" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AI42" s="16"/>
+      <c r="AI42" s="16">
+        <f t="shared" si="6"/>
+        <v>37.24</v>
+      </c>
       <c r="AJ42" s="16"/>
       <c r="AK42" s="16"/>
       <c r="AL42" s="16"/>
@@ -28605,24 +28719,24 @@
         <v>1</v>
       </c>
       <c r="L43" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M43" s="12"/>
       <c r="N43" s="12"/>
       <c r="O43" s="12"/>
       <c r="P43" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.2</v>
       </c>
       <c r="Q43" s="14"/>
       <c r="R43" s="14"/>
       <c r="S43" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-10</v>
       </c>
       <c r="T43" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-10</v>
       </c>
       <c r="U43" s="12">
@@ -28651,7 +28765,10 @@
       <c r="AF43" s="12"/>
       <c r="AG43" s="12"/>
       <c r="AH43" s="15"/>
-      <c r="AI43" s="16"/>
+      <c r="AI43" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AJ43" s="16"/>
       <c r="AK43" s="16"/>
       <c r="AL43" s="16"/>
@@ -28703,7 +28820,7 @@
         <v>215</v>
       </c>
       <c r="L44" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-23</v>
       </c>
       <c r="M44" s="16"/>
@@ -28712,23 +28829,23 @@
         <v>192</v>
       </c>
       <c r="P44" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>38.4</v>
       </c>
       <c r="Q44" s="4">
-        <f t="shared" ref="Q44:Q66" si="22">14*P44-O44-F44</f>
+        <f t="shared" ref="Q44:Q66" si="23">14*P44-O44-F44</f>
         <v>217.60000000000002</v>
       </c>
       <c r="R44" s="4">
-        <f t="shared" ref="R44:R66" si="23">AC44*AD44</f>
+        <f t="shared" ref="R44:R66" si="24">AC44*AD44</f>
         <v>192</v>
       </c>
       <c r="S44" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>13.333333333333334</v>
       </c>
       <c r="T44" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>8.3333333333333339</v>
       </c>
       <c r="U44" s="16">
@@ -28751,7 +28868,7 @@
       </c>
       <c r="AA44" s="16"/>
       <c r="AB44" s="16">
-        <f t="shared" ref="AB44:AB68" si="24">G44*Q44</f>
+        <f t="shared" ref="AB44:AB68" si="25">G44*Q44</f>
         <v>87.04000000000002</v>
       </c>
       <c r="AC44" s="6">
@@ -28759,11 +28876,11 @@
         <v>16</v>
       </c>
       <c r="AD44" s="8">
-        <f t="shared" ref="AD44:AD66" si="25">MROUND(Q44, AC44*AF44)/AC44</f>
+        <f t="shared" ref="AD44:AD66" si="26">MROUND(Q44, AC44*AF44)/AC44</f>
         <v>12</v>
       </c>
       <c r="AE44" s="16">
-        <f t="shared" ref="AE44:AE66" si="26">AD44*AC44*G44</f>
+        <f t="shared" ref="AE44:AE66" si="27">AD44*AC44*G44</f>
         <v>76.800000000000011</v>
       </c>
       <c r="AF44" s="16">
@@ -28775,10 +28892,13 @@
         <v>84</v>
       </c>
       <c r="AH44" s="8">
-        <f t="shared" ref="AH44:AH66" si="27">AD44/AG44</f>
+        <f t="shared" ref="AH44:AH66" si="28">AD44/AG44</f>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AI44" s="16"/>
+      <c r="AI44" s="16">
+        <f t="shared" si="6"/>
+        <v>15.36</v>
+      </c>
       <c r="AJ44" s="16"/>
       <c r="AK44" s="16"/>
       <c r="AL44" s="16"/>
@@ -28832,7 +28952,7 @@
         <v>325</v>
       </c>
       <c r="L45" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>69</v>
       </c>
       <c r="M45" s="16"/>
@@ -28841,23 +28961,23 @@
         <v>480</v>
       </c>
       <c r="P45" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>78.8</v>
       </c>
       <c r="Q45" s="4">
+        <f t="shared" si="23"/>
+        <v>141.20000000000005</v>
+      </c>
+      <c r="R45" s="4">
+        <f t="shared" si="24"/>
+        <v>120</v>
+      </c>
+      <c r="S45" s="16">
+        <f t="shared" si="21"/>
+        <v>13.730964467005077</v>
+      </c>
+      <c r="T45" s="16">
         <f t="shared" si="22"/>
-        <v>141.20000000000005</v>
-      </c>
-      <c r="R45" s="4">
-        <f t="shared" si="23"/>
-        <v>120</v>
-      </c>
-      <c r="S45" s="16">
-        <f t="shared" si="20"/>
-        <v>13.730964467005077</v>
-      </c>
-      <c r="T45" s="16">
-        <f t="shared" si="21"/>
         <v>12.208121827411167</v>
       </c>
       <c r="U45" s="16">
@@ -28880,7 +29000,7 @@
       </c>
       <c r="AA45" s="16"/>
       <c r="AB45" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>98.840000000000032</v>
       </c>
       <c r="AC45" s="6">
@@ -28888,11 +29008,11 @@
         <v>10</v>
       </c>
       <c r="AD45" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>12</v>
       </c>
       <c r="AE45" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>84</v>
       </c>
       <c r="AF45" s="16">
@@ -28904,10 +29024,13 @@
         <v>84</v>
       </c>
       <c r="AH45" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AI45" s="16"/>
+      <c r="AI45" s="16">
+        <f t="shared" si="6"/>
+        <v>55.16</v>
+      </c>
       <c r="AJ45" s="16"/>
       <c r="AK45" s="16"/>
       <c r="AL45" s="16"/>
@@ -28957,7 +29080,7 @@
         <v>100</v>
       </c>
       <c r="L46" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-24</v>
       </c>
       <c r="M46" s="16"/>
@@ -28966,22 +29089,22 @@
         <v>240</v>
       </c>
       <c r="P46" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>15.2</v>
       </c>
       <c r="Q46" s="4"/>
       <c r="R46" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S46" s="16">
-        <f t="shared" si="20"/>
-        <v>15.657894736842106</v>
-      </c>
-      <c r="T46" s="16">
         <f t="shared" si="21"/>
         <v>15.657894736842106</v>
       </c>
+      <c r="T46" s="16">
+        <f t="shared" si="22"/>
+        <v>15.657894736842106</v>
+      </c>
       <c r="U46" s="16">
         <v>30.2</v>
       </c>
@@ -29002,7 +29125,7 @@
       </c>
       <c r="AA46" s="16"/>
       <c r="AB46" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC46" s="6">
@@ -29010,11 +29133,11 @@
         <v>10</v>
       </c>
       <c r="AD46" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AE46" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AF46" s="16">
@@ -29026,10 +29149,13 @@
         <v>84</v>
       </c>
       <c r="AH46" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AI46" s="16"/>
+      <c r="AI46" s="16">
+        <f t="shared" si="6"/>
+        <v>10.639999999999999</v>
+      </c>
       <c r="AJ46" s="16"/>
       <c r="AK46" s="16"/>
       <c r="AL46" s="16"/>
@@ -29079,7 +29205,7 @@
         <v>646</v>
       </c>
       <c r="L47" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-17</v>
       </c>
       <c r="M47" s="16"/>
@@ -29088,7 +29214,7 @@
         <v>360</v>
       </c>
       <c r="P47" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>125.8</v>
       </c>
       <c r="Q47" s="4">
@@ -29096,15 +29222,15 @@
         <v>859.98</v>
       </c>
       <c r="R47" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>840</v>
       </c>
       <c r="S47" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>12.941176470588236</v>
       </c>
       <c r="T47" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>6.2639109697933231</v>
       </c>
       <c r="U47" s="16">
@@ -29127,7 +29253,7 @@
       </c>
       <c r="AA47" s="16"/>
       <c r="AB47" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>859.98</v>
       </c>
       <c r="AC47" s="6">
@@ -29135,11 +29261,11 @@
         <v>5</v>
       </c>
       <c r="AD47" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>168</v>
       </c>
       <c r="AE47" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>840</v>
       </c>
       <c r="AF47" s="16">
@@ -29151,10 +29277,13 @@
         <v>84</v>
       </c>
       <c r="AH47" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>2</v>
       </c>
-      <c r="AI47" s="16"/>
+      <c r="AI47" s="16">
+        <f t="shared" si="6"/>
+        <v>125.8</v>
+      </c>
       <c r="AJ47" s="16"/>
       <c r="AK47" s="16"/>
       <c r="AL47" s="16"/>
@@ -29206,7 +29335,7 @@
         <v>193</v>
       </c>
       <c r="L48" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-12</v>
       </c>
       <c r="M48" s="16"/>
@@ -29215,23 +29344,23 @@
         <v>288</v>
       </c>
       <c r="P48" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>36.200000000000003</v>
       </c>
       <c r="Q48" s="4">
+        <f t="shared" si="23"/>
+        <v>123.80000000000007</v>
+      </c>
+      <c r="R48" s="4">
+        <f t="shared" si="24"/>
+        <v>96</v>
+      </c>
+      <c r="S48" s="16">
+        <f t="shared" si="21"/>
+        <v>13.232044198895027</v>
+      </c>
+      <c r="T48" s="16">
         <f t="shared" si="22"/>
-        <v>123.80000000000007</v>
-      </c>
-      <c r="R48" s="4">
-        <f t="shared" si="23"/>
-        <v>96</v>
-      </c>
-      <c r="S48" s="16">
-        <f t="shared" si="20"/>
-        <v>13.232044198895027</v>
-      </c>
-      <c r="T48" s="16">
-        <f t="shared" si="21"/>
         <v>10.580110497237568</v>
       </c>
       <c r="U48" s="16">
@@ -29254,7 +29383,7 @@
       </c>
       <c r="AA48" s="16"/>
       <c r="AB48" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>111.42000000000006</v>
       </c>
       <c r="AC48" s="6">
@@ -29262,11 +29391,11 @@
         <v>8</v>
       </c>
       <c r="AD48" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>12</v>
       </c>
       <c r="AE48" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>86.4</v>
       </c>
       <c r="AF48" s="16">
@@ -29278,10 +29407,13 @@
         <v>84</v>
       </c>
       <c r="AH48" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AI48" s="16"/>
+      <c r="AI48" s="16">
+        <f t="shared" si="6"/>
+        <v>32.580000000000005</v>
+      </c>
       <c r="AJ48" s="16"/>
       <c r="AK48" s="16"/>
       <c r="AL48" s="16"/>
@@ -29331,7 +29463,7 @@
         <v>86</v>
       </c>
       <c r="L49" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-7</v>
       </c>
       <c r="M49" s="16"/>
@@ -29340,7 +29472,7 @@
         <v>96</v>
       </c>
       <c r="P49" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>15.8</v>
       </c>
       <c r="Q49" s="4">
@@ -29348,15 +29480,15 @@
         <v>55.800000000000011</v>
       </c>
       <c r="R49" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>96</v>
       </c>
       <c r="S49" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>18.544303797468352</v>
       </c>
       <c r="T49" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>12.468354430379746</v>
       </c>
       <c r="U49" s="16">
@@ -29379,7 +29511,7 @@
       </c>
       <c r="AA49" s="16"/>
       <c r="AB49" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>50.220000000000013</v>
       </c>
       <c r="AC49" s="6">
@@ -29387,11 +29519,11 @@
         <v>8</v>
       </c>
       <c r="AD49" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>12</v>
       </c>
       <c r="AE49" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>86.4</v>
       </c>
       <c r="AF49" s="16">
@@ -29403,10 +29535,13 @@
         <v>84</v>
       </c>
       <c r="AH49" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AI49" s="16"/>
+      <c r="AI49" s="16">
+        <f t="shared" si="6"/>
+        <v>14.22</v>
+      </c>
       <c r="AJ49" s="16"/>
       <c r="AK49" s="16"/>
       <c r="AL49" s="16"/>
@@ -29456,7 +29591,7 @@
         <v>330</v>
       </c>
       <c r="L50" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M50" s="16"/>
@@ -29465,23 +29600,23 @@
         <v>420</v>
       </c>
       <c r="P50" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>66</v>
       </c>
       <c r="Q50" s="4">
+        <f t="shared" si="23"/>
+        <v>259</v>
+      </c>
+      <c r="R50" s="4">
+        <f t="shared" si="24"/>
+        <v>240</v>
+      </c>
+      <c r="S50" s="16">
+        <f t="shared" si="21"/>
+        <v>13.712121212121213</v>
+      </c>
+      <c r="T50" s="16">
         <f t="shared" si="22"/>
-        <v>259</v>
-      </c>
-      <c r="R50" s="4">
-        <f t="shared" si="23"/>
-        <v>240</v>
-      </c>
-      <c r="S50" s="16">
-        <f t="shared" si="20"/>
-        <v>13.712121212121213</v>
-      </c>
-      <c r="T50" s="16">
-        <f t="shared" si="21"/>
         <v>10.075757575757576</v>
       </c>
       <c r="U50" s="16">
@@ -29504,7 +29639,7 @@
       </c>
       <c r="AA50" s="16"/>
       <c r="AB50" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>259</v>
       </c>
       <c r="AC50" s="6">
@@ -29512,11 +29647,11 @@
         <v>5</v>
       </c>
       <c r="AD50" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>48</v>
       </c>
       <c r="AE50" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>240</v>
       </c>
       <c r="AF50" s="16">
@@ -29528,10 +29663,13 @@
         <v>144</v>
       </c>
       <c r="AH50" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AI50" s="16"/>
+      <c r="AI50" s="16">
+        <f t="shared" si="6"/>
+        <v>66</v>
+      </c>
       <c r="AJ50" s="16"/>
       <c r="AK50" s="16"/>
       <c r="AL50" s="16"/>
@@ -29581,7 +29719,7 @@
         <v>292</v>
       </c>
       <c r="L51" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-3.6999999999999886</v>
       </c>
       <c r="M51" s="16"/>
@@ -29590,23 +29728,23 @@
         <v>725.2</v>
       </c>
       <c r="P51" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>57.660000000000004</v>
       </c>
       <c r="Q51" s="4">
+        <f t="shared" si="23"/>
+        <v>163.83999999999997</v>
+      </c>
+      <c r="R51" s="4">
+        <f t="shared" si="24"/>
+        <v>155.4</v>
+      </c>
+      <c r="S51" s="16">
+        <f t="shared" si="21"/>
+        <v>13.853624696496706</v>
+      </c>
+      <c r="T51" s="16">
         <f t="shared" si="22"/>
-        <v>163.83999999999997</v>
-      </c>
-      <c r="R51" s="4">
-        <f t="shared" si="23"/>
-        <v>155.4</v>
-      </c>
-      <c r="S51" s="16">
-        <f t="shared" si="20"/>
-        <v>13.853624696496706</v>
-      </c>
-      <c r="T51" s="16">
-        <f t="shared" si="21"/>
         <v>11.158515435310441</v>
       </c>
       <c r="U51" s="16">
@@ -29629,7 +29767,7 @@
       </c>
       <c r="AA51" s="16"/>
       <c r="AB51" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>163.83999999999997</v>
       </c>
       <c r="AC51" s="6">
@@ -29637,11 +29775,11 @@
         <v>3.7</v>
       </c>
       <c r="AD51" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>42</v>
       </c>
       <c r="AE51" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>155.4</v>
       </c>
       <c r="AF51" s="16">
@@ -29653,10 +29791,13 @@
         <v>126</v>
       </c>
       <c r="AH51" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AI51" s="16"/>
+      <c r="AI51" s="16">
+        <f t="shared" si="6"/>
+        <v>57.660000000000004</v>
+      </c>
       <c r="AJ51" s="16"/>
       <c r="AK51" s="16"/>
       <c r="AL51" s="16"/>
@@ -29703,7 +29844,7 @@
         <v>542</v>
       </c>
       <c r="L52" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="M52" s="16"/>
@@ -29712,7 +29853,7 @@
         <v>0</v>
       </c>
       <c r="P52" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>108.6</v>
       </c>
       <c r="Q52" s="4">
@@ -29720,15 +29861,15 @@
         <v>1146.6599999999999</v>
       </c>
       <c r="R52" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1260</v>
       </c>
       <c r="S52" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>14.14364640883978</v>
       </c>
       <c r="T52" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2.541436464088398</v>
       </c>
       <c r="U52" s="16">
@@ -29753,18 +29894,18 @@
         <v>92</v>
       </c>
       <c r="AB52" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>103.19939999999998</v>
       </c>
       <c r="AC52" s="6">
         <v>30</v>
       </c>
       <c r="AD52" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>42</v>
       </c>
       <c r="AE52" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>113.39999999999999</v>
       </c>
       <c r="AF52" s="16">
@@ -29774,10 +29915,13 @@
         <v>126</v>
       </c>
       <c r="AH52" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AI52" s="16"/>
+      <c r="AI52" s="16">
+        <f t="shared" si="6"/>
+        <v>9.7739999999999991</v>
+      </c>
       <c r="AJ52" s="16"/>
       <c r="AK52" s="16"/>
       <c r="AL52" s="16"/>
@@ -29827,7 +29971,7 @@
         <v>92</v>
       </c>
       <c r="L53" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-18</v>
       </c>
       <c r="M53" s="16"/>
@@ -29836,22 +29980,22 @@
         <v>336</v>
       </c>
       <c r="P53" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>14.8</v>
       </c>
       <c r="Q53" s="4"/>
       <c r="R53" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S53" s="16">
-        <f t="shared" si="20"/>
-        <v>21.95945945945946</v>
-      </c>
-      <c r="T53" s="16">
         <f t="shared" si="21"/>
         <v>21.95945945945946</v>
       </c>
+      <c r="T53" s="16">
+        <f t="shared" si="22"/>
+        <v>21.95945945945946</v>
+      </c>
       <c r="U53" s="16">
         <v>32.6</v>
       </c>
@@ -29872,7 +30016,7 @@
       </c>
       <c r="AA53" s="16"/>
       <c r="AB53" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC53" s="6">
@@ -29880,11 +30024,11 @@
         <v>6</v>
       </c>
       <c r="AD53" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AE53" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AF53" s="16">
@@ -29896,10 +30040,13 @@
         <v>140</v>
       </c>
       <c r="AH53" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AI53" s="16"/>
+      <c r="AI53" s="16">
+        <f t="shared" si="6"/>
+        <v>3.4040000000000004</v>
+      </c>
       <c r="AJ53" s="16"/>
       <c r="AK53" s="16"/>
       <c r="AL53" s="16"/>
@@ -29951,7 +30098,7 @@
         <v>715</v>
       </c>
       <c r="L54" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-69</v>
       </c>
       <c r="M54" s="16"/>
@@ -29960,7 +30107,7 @@
         <v>504</v>
       </c>
       <c r="P54" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>129.19999999999999</v>
       </c>
       <c r="Q54" s="4">
@@ -29968,15 +30115,15 @@
         <v>412.51999999999975</v>
       </c>
       <c r="R54" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>336</v>
       </c>
       <c r="S54" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>12.507739938080496</v>
       </c>
       <c r="T54" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>9.9071207430340564</v>
       </c>
       <c r="U54" s="16">
@@ -29999,7 +30146,7 @@
       </c>
       <c r="AA54" s="16"/>
       <c r="AB54" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>103.12999999999994</v>
       </c>
       <c r="AC54" s="6">
@@ -30007,11 +30154,11 @@
         <v>12</v>
       </c>
       <c r="AD54" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>28</v>
       </c>
       <c r="AE54" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>84</v>
       </c>
       <c r="AF54" s="16">
@@ -30023,10 +30170,13 @@
         <v>70</v>
       </c>
       <c r="AH54" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.4</v>
       </c>
-      <c r="AI54" s="16"/>
+      <c r="AI54" s="16">
+        <f t="shared" si="6"/>
+        <v>32.299999999999997</v>
+      </c>
       <c r="AJ54" s="16"/>
       <c r="AK54" s="16"/>
       <c r="AL54" s="16"/>
@@ -30076,7 +30226,7 @@
         <v>440</v>
       </c>
       <c r="L55" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-20</v>
       </c>
       <c r="M55" s="16"/>
@@ -30085,23 +30235,23 @@
         <v>168</v>
       </c>
       <c r="P55" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>84</v>
       </c>
       <c r="Q55" s="4">
+        <f t="shared" si="23"/>
+        <v>540</v>
+      </c>
+      <c r="R55" s="4">
+        <f t="shared" si="24"/>
+        <v>504</v>
+      </c>
+      <c r="S55" s="16">
+        <f t="shared" si="21"/>
+        <v>13.571428571428571</v>
+      </c>
+      <c r="T55" s="16">
         <f t="shared" si="22"/>
-        <v>540</v>
-      </c>
-      <c r="R55" s="4">
-        <f t="shared" si="23"/>
-        <v>504</v>
-      </c>
-      <c r="S55" s="16">
-        <f t="shared" si="20"/>
-        <v>13.571428571428571</v>
-      </c>
-      <c r="T55" s="16">
-        <f t="shared" si="21"/>
         <v>7.5714285714285712</v>
       </c>
       <c r="U55" s="16">
@@ -30124,7 +30274,7 @@
       </c>
       <c r="AA55" s="16"/>
       <c r="AB55" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>135</v>
       </c>
       <c r="AC55" s="6">
@@ -30132,11 +30282,11 @@
         <v>12</v>
       </c>
       <c r="AD55" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>42</v>
       </c>
       <c r="AE55" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>126</v>
       </c>
       <c r="AF55" s="16">
@@ -30148,10 +30298,13 @@
         <v>70</v>
       </c>
       <c r="AH55" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.6</v>
       </c>
-      <c r="AI55" s="16"/>
+      <c r="AI55" s="16">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
       <c r="AJ55" s="16"/>
       <c r="AK55" s="16"/>
       <c r="AL55" s="16"/>
@@ -30203,7 +30356,7 @@
         <v>23</v>
       </c>
       <c r="L56" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-1</v>
       </c>
       <c r="M56" s="16"/>
@@ -30212,22 +30365,22 @@
         <v>0</v>
       </c>
       <c r="P56" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="Q56" s="4"/>
       <c r="R56" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S56" s="16">
-        <f t="shared" si="20"/>
-        <v>14.318181818181817</v>
-      </c>
-      <c r="T56" s="16">
         <f t="shared" si="21"/>
         <v>14.318181818181817</v>
       </c>
+      <c r="T56" s="16">
+        <f t="shared" si="22"/>
+        <v>14.318181818181817</v>
+      </c>
       <c r="U56" s="16">
         <v>7.2</v>
       </c>
@@ -30248,7 +30401,7 @@
       </c>
       <c r="AA56" s="16"/>
       <c r="AB56" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC56" s="6">
@@ -30256,11 +30409,11 @@
         <v>6</v>
       </c>
       <c r="AD56" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AE56" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AF56" s="16">
@@ -30272,10 +30425,13 @@
         <v>140</v>
       </c>
       <c r="AH56" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AI56" s="16"/>
+      <c r="AI56" s="16">
+        <f t="shared" si="6"/>
+        <v>0.79200000000000004</v>
+      </c>
       <c r="AJ56" s="16"/>
       <c r="AK56" s="16"/>
       <c r="AL56" s="16"/>
@@ -30325,7 +30481,7 @@
         <v>28</v>
       </c>
       <c r="L57" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M57" s="16"/>
@@ -30334,22 +30490,22 @@
         <v>84</v>
       </c>
       <c r="P57" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>5.6</v>
       </c>
       <c r="Q57" s="4"/>
       <c r="R57" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S57" s="16">
-        <f t="shared" si="20"/>
-        <v>21.964285714285715</v>
-      </c>
-      <c r="T57" s="16">
         <f t="shared" si="21"/>
         <v>21.964285714285715</v>
       </c>
+      <c r="T57" s="16">
+        <f t="shared" si="22"/>
+        <v>21.964285714285715</v>
+      </c>
       <c r="U57" s="16">
         <v>9.6</v>
       </c>
@@ -30370,7 +30526,7 @@
       </c>
       <c r="AA57" s="16"/>
       <c r="AB57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC57" s="6">
@@ -30378,11 +30534,11 @@
         <v>6</v>
       </c>
       <c r="AD57" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AE57" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AF57" s="16">
@@ -30394,10 +30550,13 @@
         <v>140</v>
       </c>
       <c r="AH57" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AI57" s="16"/>
+      <c r="AI57" s="16">
+        <f t="shared" si="6"/>
+        <v>1.008</v>
+      </c>
       <c r="AJ57" s="16"/>
       <c r="AK57" s="16"/>
       <c r="AL57" s="16"/>
@@ -30439,7 +30598,7 @@
       <c r="J58" s="16"/>
       <c r="K58" s="16"/>
       <c r="L58" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M58" s="16"/>
@@ -30448,22 +30607,22 @@
         <v>84</v>
       </c>
       <c r="P58" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q58" s="4"/>
       <c r="R58" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S58" s="16" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T58" s="16" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="T58" s="16" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="U58" s="16">
         <v>0</v>
       </c>
@@ -30484,7 +30643,7 @@
       </c>
       <c r="AA58" s="16"/>
       <c r="AB58" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC58" s="6">
@@ -30492,11 +30651,11 @@
         <v>6</v>
       </c>
       <c r="AD58" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AE58" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AF58" s="16">
@@ -30508,10 +30667,13 @@
         <v>140</v>
       </c>
       <c r="AH58" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AI58" s="16"/>
+      <c r="AI58" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AJ58" s="16"/>
       <c r="AK58" s="16"/>
       <c r="AL58" s="16"/>
@@ -30561,7 +30723,7 @@
         <v>600</v>
       </c>
       <c r="L59" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-31</v>
       </c>
       <c r="M59" s="16"/>
@@ -30570,7 +30732,7 @@
         <v>672</v>
       </c>
       <c r="P59" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>113.8</v>
       </c>
       <c r="Q59" s="4">
@@ -30578,15 +30740,15 @@
         <v>495.78</v>
       </c>
       <c r="R59" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>504</v>
       </c>
       <c r="S59" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>13.172231985940247</v>
       </c>
       <c r="T59" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>8.743409490333919</v>
       </c>
       <c r="U59" s="16">
@@ -30609,7 +30771,7 @@
       </c>
       <c r="AA59" s="16"/>
       <c r="AB59" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>148.73399999999998</v>
       </c>
       <c r="AC59" s="6">
@@ -30617,11 +30779,11 @@
         <v>12</v>
       </c>
       <c r="AD59" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>42</v>
       </c>
       <c r="AE59" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>151.19999999999999</v>
       </c>
       <c r="AF59" s="16">
@@ -30633,10 +30795,13 @@
         <v>70</v>
       </c>
       <c r="AH59" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.6</v>
       </c>
-      <c r="AI59" s="16"/>
+      <c r="AI59" s="16">
+        <f t="shared" si="6"/>
+        <v>34.14</v>
+      </c>
       <c r="AJ59" s="16"/>
       <c r="AK59" s="16"/>
       <c r="AL59" s="16"/>
@@ -30686,7 +30851,7 @@
         <v>535</v>
       </c>
       <c r="L60" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-39</v>
       </c>
       <c r="M60" s="16"/>
@@ -30695,23 +30860,23 @@
         <v>0</v>
       </c>
       <c r="P60" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>99.2</v>
       </c>
       <c r="Q60" s="4">
+        <f t="shared" si="23"/>
+        <v>370.79999999999995</v>
+      </c>
+      <c r="R60" s="4">
+        <f t="shared" si="24"/>
+        <v>336</v>
+      </c>
+      <c r="S60" s="16">
+        <f t="shared" si="21"/>
+        <v>13.649193548387096</v>
+      </c>
+      <c r="T60" s="16">
         <f t="shared" si="22"/>
-        <v>370.79999999999995</v>
-      </c>
-      <c r="R60" s="4">
-        <f t="shared" si="23"/>
-        <v>336</v>
-      </c>
-      <c r="S60" s="16">
-        <f t="shared" si="20"/>
-        <v>13.649193548387096</v>
-      </c>
-      <c r="T60" s="16">
-        <f t="shared" si="21"/>
         <v>10.262096774193548</v>
       </c>
       <c r="U60" s="16">
@@ -30734,7 +30899,7 @@
       </c>
       <c r="AA60" s="16"/>
       <c r="AB60" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>111.23999999999998</v>
       </c>
       <c r="AC60" s="6">
@@ -30742,11 +30907,11 @@
         <v>12</v>
       </c>
       <c r="AD60" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>28</v>
       </c>
       <c r="AE60" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>100.8</v>
       </c>
       <c r="AF60" s="16">
@@ -30758,10 +30923,13 @@
         <v>70</v>
       </c>
       <c r="AH60" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.4</v>
       </c>
-      <c r="AI60" s="16"/>
+      <c r="AI60" s="16">
+        <f t="shared" si="6"/>
+        <v>29.759999999999998</v>
+      </c>
       <c r="AJ60" s="16"/>
       <c r="AK60" s="16"/>
       <c r="AL60" s="16"/>
@@ -30811,7 +30979,7 @@
         <v>88</v>
       </c>
       <c r="L61" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-12</v>
       </c>
       <c r="M61" s="16"/>
@@ -30820,22 +30988,22 @@
         <v>0</v>
       </c>
       <c r="P61" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>15.2</v>
       </c>
       <c r="Q61" s="4"/>
       <c r="R61" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S61" s="16">
-        <f t="shared" si="20"/>
-        <v>18.421052631578949</v>
-      </c>
-      <c r="T61" s="16">
         <f t="shared" si="21"/>
         <v>18.421052631578949</v>
       </c>
+      <c r="T61" s="16">
+        <f t="shared" si="22"/>
+        <v>18.421052631578949</v>
+      </c>
       <c r="U61" s="16">
         <v>25.8</v>
       </c>
@@ -30856,7 +31024,7 @@
       </c>
       <c r="AA61" s="16"/>
       <c r="AB61" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC61" s="6">
@@ -30864,11 +31032,11 @@
         <v>14</v>
       </c>
       <c r="AD61" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AE61" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AF61" s="16">
@@ -30880,10 +31048,13 @@
         <v>70</v>
       </c>
       <c r="AH61" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AI61" s="16"/>
+      <c r="AI61" s="16">
+        <f t="shared" si="6"/>
+        <v>4.5599999999999996</v>
+      </c>
       <c r="AJ61" s="16"/>
       <c r="AK61" s="16"/>
       <c r="AL61" s="16"/>
@@ -30933,7 +31104,7 @@
         <v>1619</v>
       </c>
       <c r="L62" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-569</v>
       </c>
       <c r="M62" s="16"/>
@@ -30942,23 +31113,23 @@
         <v>2520</v>
       </c>
       <c r="P62" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>210</v>
       </c>
       <c r="Q62" s="4">
-        <f t="shared" ref="Q62:Q63" si="28">$Q$1*P62-O62-F62</f>
+        <f t="shared" ref="Q62:Q63" si="29">$Q$1*P62-O62-F62</f>
         <v>248</v>
       </c>
       <c r="R62" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>168</v>
       </c>
       <c r="S62" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>12.719047619047618</v>
       </c>
       <c r="T62" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>11.919047619047619</v>
       </c>
       <c r="U62" s="16">
@@ -30981,7 +31152,7 @@
       </c>
       <c r="AA62" s="16"/>
       <c r="AB62" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>62</v>
       </c>
       <c r="AC62" s="6">
@@ -30989,11 +31160,11 @@
         <v>12</v>
       </c>
       <c r="AD62" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>14</v>
       </c>
       <c r="AE62" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>42</v>
       </c>
       <c r="AF62" s="16">
@@ -31005,10 +31176,13 @@
         <v>70</v>
       </c>
       <c r="AH62" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.2</v>
       </c>
-      <c r="AI62" s="16"/>
+      <c r="AI62" s="16">
+        <f t="shared" si="6"/>
+        <v>52.5</v>
+      </c>
       <c r="AJ62" s="16"/>
       <c r="AK62" s="16"/>
       <c r="AL62" s="16"/>
@@ -31060,7 +31234,7 @@
         <v>1635</v>
       </c>
       <c r="L63" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>43</v>
       </c>
       <c r="M63" s="16"/>
@@ -31069,23 +31243,23 @@
         <v>1344</v>
       </c>
       <c r="P63" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>335.6</v>
       </c>
       <c r="Q63" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1208.3600000000006</v>
       </c>
       <c r="R63" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1176</v>
       </c>
       <c r="S63" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>13.003575685339689</v>
       </c>
       <c r="T63" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>9.4994040524433849</v>
       </c>
       <c r="U63" s="16">
@@ -31108,7 +31282,7 @@
       </c>
       <c r="AA63" s="16"/>
       <c r="AB63" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>302.09000000000015</v>
       </c>
       <c r="AC63" s="6">
@@ -31116,11 +31290,11 @@
         <v>12</v>
       </c>
       <c r="AD63" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>98</v>
       </c>
       <c r="AE63" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>294</v>
       </c>
       <c r="AF63" s="16">
@@ -31132,10 +31306,13 @@
         <v>70</v>
       </c>
       <c r="AH63" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1.4</v>
       </c>
-      <c r="AI63" s="16"/>
+      <c r="AI63" s="16">
+        <f t="shared" si="6"/>
+        <v>83.9</v>
+      </c>
       <c r="AJ63" s="16"/>
       <c r="AK63" s="16"/>
       <c r="AL63" s="16"/>
@@ -31185,7 +31362,7 @@
         <v>286</v>
       </c>
       <c r="L64" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-81</v>
       </c>
       <c r="M64" s="16"/>
@@ -31194,23 +31371,23 @@
         <v>504</v>
       </c>
       <c r="P64" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>41</v>
       </c>
       <c r="Q64" s="4">
+        <f t="shared" si="23"/>
+        <v>71</v>
+      </c>
+      <c r="R64" s="4">
+        <f t="shared" si="24"/>
+        <v>84</v>
+      </c>
+      <c r="S64" s="16">
+        <f t="shared" si="21"/>
+        <v>14.317073170731707</v>
+      </c>
+      <c r="T64" s="16">
         <f t="shared" si="22"/>
-        <v>71</v>
-      </c>
-      <c r="R64" s="4">
-        <f t="shared" si="23"/>
-        <v>84</v>
-      </c>
-      <c r="S64" s="16">
-        <f t="shared" si="20"/>
-        <v>14.317073170731707</v>
-      </c>
-      <c r="T64" s="16">
-        <f t="shared" si="21"/>
         <v>12.268292682926829</v>
       </c>
       <c r="U64" s="16">
@@ -31233,7 +31410,7 @@
       </c>
       <c r="AA64" s="16"/>
       <c r="AB64" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>16.330000000000002</v>
       </c>
       <c r="AC64" s="6">
@@ -31241,11 +31418,11 @@
         <v>6</v>
       </c>
       <c r="AD64" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>14</v>
       </c>
       <c r="AE64" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>19.32</v>
       </c>
       <c r="AF64" s="16">
@@ -31257,10 +31434,13 @@
         <v>140</v>
       </c>
       <c r="AH64" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.1</v>
       </c>
-      <c r="AI64" s="16"/>
+      <c r="AI64" s="16">
+        <f t="shared" si="6"/>
+        <v>9.43</v>
+      </c>
       <c r="AJ64" s="16"/>
       <c r="AK64" s="16"/>
       <c r="AL64" s="16"/>
@@ -31308,7 +31488,7 @@
         <v>213.3</v>
       </c>
       <c r="L65" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-153.9</v>
       </c>
       <c r="M65" s="16"/>
@@ -31317,22 +31497,22 @@
         <v>378</v>
       </c>
       <c r="P65" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11.879999999999999</v>
       </c>
       <c r="Q65" s="4"/>
       <c r="R65" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S65" s="16">
-        <f t="shared" si="20"/>
-        <v>31.81818181818182</v>
-      </c>
-      <c r="T65" s="16">
         <f t="shared" si="21"/>
         <v>31.81818181818182</v>
       </c>
+      <c r="T65" s="16">
+        <f t="shared" si="22"/>
+        <v>31.81818181818182</v>
+      </c>
       <c r="U65" s="16">
         <v>42.12</v>
       </c>
@@ -31353,7 +31533,7 @@
       </c>
       <c r="AA65" s="16"/>
       <c r="AB65" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC65" s="6">
@@ -31361,11 +31541,11 @@
         <v>2.7</v>
       </c>
       <c r="AD65" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AE65" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AF65" s="16">
@@ -31377,10 +31557,13 @@
         <v>126</v>
       </c>
       <c r="AH65" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AI65" s="16"/>
+      <c r="AI65" s="16">
+        <f t="shared" si="6"/>
+        <v>11.879999999999999</v>
+      </c>
       <c r="AJ65" s="16"/>
       <c r="AK65" s="16"/>
       <c r="AL65" s="16"/>
@@ -31432,7 +31615,7 @@
         <v>745</v>
       </c>
       <c r="L66" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-305</v>
       </c>
       <c r="M66" s="16"/>
@@ -31441,23 +31624,23 @@
         <v>1140</v>
       </c>
       <c r="P66" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>88</v>
       </c>
       <c r="Q66" s="4">
+        <f t="shared" si="23"/>
+        <v>97</v>
+      </c>
+      <c r="R66" s="4">
+        <f t="shared" si="24"/>
+        <v>120</v>
+      </c>
+      <c r="S66" s="16">
+        <f t="shared" si="21"/>
+        <v>14.261363636363637</v>
+      </c>
+      <c r="T66" s="16">
         <f t="shared" si="22"/>
-        <v>97</v>
-      </c>
-      <c r="R66" s="4">
-        <f t="shared" si="23"/>
-        <v>120</v>
-      </c>
-      <c r="S66" s="16">
-        <f t="shared" si="20"/>
-        <v>14.261363636363637</v>
-      </c>
-      <c r="T66" s="16">
-        <f t="shared" si="21"/>
         <v>12.897727272727273</v>
       </c>
       <c r="U66" s="16">
@@ -31480,7 +31663,7 @@
       </c>
       <c r="AA66" s="16"/>
       <c r="AB66" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>97</v>
       </c>
       <c r="AC66" s="6">
@@ -31488,11 +31671,11 @@
         <v>5</v>
       </c>
       <c r="AD66" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>24</v>
       </c>
       <c r="AE66" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>120</v>
       </c>
       <c r="AF66" s="16">
@@ -31504,10 +31687,13 @@
         <v>84</v>
       </c>
       <c r="AH66" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="AI66" s="16"/>
+      <c r="AI66" s="16">
+        <f t="shared" si="6"/>
+        <v>88</v>
+      </c>
       <c r="AJ66" s="16"/>
       <c r="AK66" s="16"/>
       <c r="AL66" s="16"/>
@@ -31552,24 +31738,24 @@
       </c>
       <c r="K67" s="12"/>
       <c r="L67" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M67" s="12"/>
       <c r="N67" s="12"/>
       <c r="O67" s="12"/>
       <c r="P67" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q67" s="14"/>
       <c r="R67" s="14"/>
       <c r="S67" s="12" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T67" s="12" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U67" s="12">
@@ -31598,7 +31784,10 @@
       <c r="AF67" s="12"/>
       <c r="AG67" s="12"/>
       <c r="AH67" s="15"/>
-      <c r="AI67" s="16"/>
+      <c r="AI67" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AJ67" s="16"/>
       <c r="AK67" s="16"/>
       <c r="AL67" s="16"/>
@@ -31643,7 +31832,7 @@
         <v>300</v>
       </c>
       <c r="R68" s="4">
-        <f t="shared" ref="R68" si="29">AC68*AD68</f>
+        <f t="shared" ref="R68" si="30">AC68*AD68</f>
         <v>288</v>
       </c>
       <c r="S68" s="16"/>
@@ -31668,18 +31857,18 @@
       </c>
       <c r="AA68" s="16"/>
       <c r="AB68" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>240</v>
       </c>
       <c r="AC68" s="6">
         <v>8</v>
       </c>
       <c r="AD68" s="8">
-        <f t="shared" ref="AD68" si="30">MROUND(Q68, AC68*AF68)/AC68</f>
+        <f t="shared" ref="AD68" si="31">MROUND(Q68, AC68*AF68)/AC68</f>
         <v>36</v>
       </c>
       <c r="AE68" s="16">
-        <f t="shared" ref="AE68" si="31">AD68*AC68*G68</f>
+        <f t="shared" ref="AE68" si="32">AD68*AC68*G68</f>
         <v>230.4</v>
       </c>
       <c r="AF68" s="16">
@@ -31689,7 +31878,7 @@
         <v>84</v>
       </c>
       <c r="AH68" s="8">
-        <f t="shared" ref="AH68" si="32">AD68/AG68</f>
+        <f t="shared" ref="AH68" si="33">AD68/AG68</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="AI68" s="16"/>
